--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260731.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>17,001,000</t>
+          <t>3,577,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,577,000</t>
+          <t>17,001,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>16,986,000</t>
+          <t>15,635,648</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>15,635,648</t>
+          <t>16,986,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>4,769,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>4,769,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
